--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/FLORIDA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/FLORIDA_2017.xlsx
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C157">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C208">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C352">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C799">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C928">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C929">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C986">
